--- a/mode_docx_gen/pmi_ka2/ka_modes/КА_36.xlsx
+++ b/mode_docx_gen/pmi_ka2/ka_modes/КА_36.xlsx
@@ -653,8 +653,8 @@
       <c r="P2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q2" s="2" t="n">
-        <v>1</v>
+      <c r="Q2" t="n">
+        <v>0</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>1</v>
@@ -1101,8 +1101,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
+      <c r="A2" t="n">
+        <v>0</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
@@ -1185,17 +1185,17 @@
       <c r="AB2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AC2" s="2" t="n">
-        <v>1</v>
+      <c r="AC2" t="n">
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
       </c>
-      <c r="AE2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -1487,16 +1487,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>0</t>
@@ -1512,9 +1512,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1547,19 +1547,19 @@
           <t>0</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1592,9 +1592,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -1602,34 +1602,34 @@
           <t>0</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" s="2" t="inlineStr">
+      <c r="X2" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Z2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr">
+      <c r="AA2" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -1642,9 +1642,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="AF2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1677,9 +1677,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="AM2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
